--- a/tools/importer/reports/import-leadership-v1.report.xlsx
+++ b/tools/importer/reports/import-leadership-v1.report.xlsx
@@ -1224,7 +1224,7 @@
     <t>leadership</t>
   </si>
   <si>
-    <t>2026-09-08T05:50:35.339Z</t>
+    <t>2026-09-08T06:19:52.848Z</t>
   </si>
   <si>
     <t>Leadership &amp; Staff</t>
